--- a/GATEWAY/A1#111#DOCPLANNERXX/DOCPLANNER_ITALY/MioDottore/1/report-checklist.xlsx
+++ b/GATEWAY/A1#111#DOCPLANNERXX/DOCPLANNER_ITALY/MioDottore/1/report-checklist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincenzo.camerino/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincenzo.camerino/Documents/Obsidian notes/GIPO/SSN/FSE 2.0/Accreditamento GTW/Accreditamento MioDottore/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC2D58E-F4F0-2342-9641-0733FE7DE99F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BAD4ACE-FC58-9447-BAA4-F2FF8B770BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19220" yWindow="620" windowWidth="19200" windowHeight="19220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="600" windowWidth="19160" windowHeight="19220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="672">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -2467,9 +2467,6 @@
     <t>2.16.840.1.113883.2.9.2.120.4.4.734ae79b11c0faf2e45a2d203389199632f56537e94dc6d781425edd89c5665c.d6999cb02e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
-    <t>L'applicativo non gestisce participant, di conseguenza non è possibile valorizzare erroneamente il campo code</t>
-  </si>
-  <si>
     <t>L'identificativo della ricetta viene sempre riportato in inFulFillmentOf</t>
   </si>
   <si>
@@ -2488,9 +2485,6 @@
     <t>Sezioni opzionali non gestite</t>
   </si>
   <si>
-    <t>Non supportata la forma codificata del quesito diagnostico</t>
-  </si>
-  <si>
     <t>02/16/2026 13:37:36 +00:00</t>
   </si>
   <si>
@@ -2540,6 +2534,9 @@
   </si>
   <si>
     <t>L'applicativo non consente la registrazione di codici non previsti</t>
+  </si>
+  <si>
+    <t>Dopo un certo numero di tentativi falliti, l'operatore di backoffice avrà la possibilità di risolvere l'anomalia e ricollocare manualmente il documento nella coda di invio a FSE</t>
   </si>
 </sst>
 </file>
@@ -2701,7 +2698,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -3103,12 +3100,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3267,6 +3277,24 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="22" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3288,18 +3316,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4779,14 +4795,14 @@
       <c r="W1" s="9"/>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="64" t="s">
+      <c r="B2" s="69"/>
+      <c r="C2" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="D2" s="63"/>
+      <c r="D2" s="69"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
@@ -4807,14 +4823,14 @@
       <c r="W2" s="9"/>
     </row>
     <row r="3" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="66"/>
-      <c r="C3" s="71" t="s">
+      <c r="B3" s="72"/>
+      <c r="C3" s="77" t="s">
         <v>630</v>
       </c>
-      <c r="D3" s="63"/>
+      <c r="D3" s="69"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -4835,12 +4851,12 @@
       <c r="W3" s="9"/>
     </row>
     <row r="4" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="71" t="s">
+      <c r="A4" s="73"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="77" t="s">
         <v>631</v>
       </c>
-      <c r="D4" s="63"/>
+      <c r="D4" s="69"/>
       <c r="E4" s="4"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -4862,12 +4878,12 @@
       <c r="W4" s="9"/>
     </row>
     <row r="5" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="69"/>
-      <c r="B5" s="70"/>
-      <c r="C5" s="71" t="s">
+      <c r="A5" s="75"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="77" t="s">
         <v>632</v>
       </c>
-      <c r="D5" s="63"/>
+      <c r="D5" s="69"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -4888,8 +4904,8 @@
       <c r="W5" s="9"/>
     </row>
     <row r="6" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="60"/>
-      <c r="B6" s="61"/>
+      <c r="A6" s="66"/>
+      <c r="B6" s="67"/>
       <c r="C6" s="10"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -5191,7 +5207,7 @@
       <c r="F14" s="31">
         <v>46065</v>
       </c>
-      <c r="G14" s="72">
+      <c r="G14" s="60">
         <v>46065.517361111109</v>
       </c>
       <c r="H14" s="31" t="s">
@@ -5203,13 +5219,25 @@
       </c>
       <c r="K14" s="32"/>
       <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="32"/>
+      <c r="M14" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="N14" s="32" t="s">
+        <v>75</v>
+      </c>
       <c r="O14" s="32"/>
-      <c r="P14" s="32"/>
-      <c r="Q14" s="32"/>
-      <c r="R14" s="32"/>
-      <c r="S14" s="32"/>
+      <c r="P14" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q14" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="R14" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="S14" s="32" t="s">
+        <v>671</v>
+      </c>
       <c r="T14" s="32"/>
       <c r="U14" s="33"/>
       <c r="V14" s="34"/>
@@ -5236,10 +5264,10 @@
       <c r="F15" s="31">
         <v>46065</v>
       </c>
-      <c r="G15" s="72">
+      <c r="G15" s="60">
         <v>46065.523865740739</v>
       </c>
-      <c r="H15" s="73" t="s">
+      <c r="H15" s="61" t="s">
         <v>634</v>
       </c>
       <c r="I15" s="36"/>
@@ -5503,7 +5531,7 @@
       <c r="F22" s="31">
         <v>46065</v>
       </c>
-      <c r="G22" s="72">
+      <c r="G22" s="60">
         <v>46065.586111111108</v>
       </c>
       <c r="H22" s="31" t="s">
@@ -5515,13 +5543,25 @@
       </c>
       <c r="K22" s="32"/>
       <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="32"/>
+      <c r="M22" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="N22" s="32" t="s">
+        <v>75</v>
+      </c>
       <c r="O22" s="32"/>
-      <c r="P22" s="32"/>
-      <c r="Q22" s="32"/>
-      <c r="R22" s="32"/>
-      <c r="S22" s="32"/>
+      <c r="P22" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q22" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="R22" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="S22" s="32" t="s">
+        <v>671</v>
+      </c>
       <c r="T22" s="32"/>
       <c r="U22" s="33"/>
       <c r="V22" s="34"/>
@@ -5548,7 +5588,7 @@
       <c r="F23" s="31">
         <v>46065</v>
       </c>
-      <c r="G23" s="74" t="s">
+      <c r="G23" s="62" t="s">
         <v>636</v>
       </c>
       <c r="H23" s="31" t="s">
@@ -5835,7 +5875,7 @@
       <c r="N30" s="32" t="s">
         <v>541</v>
       </c>
-      <c r="O30" s="75" t="s">
+      <c r="O30" s="63" t="s">
         <v>638</v>
       </c>
       <c r="P30" s="32" t="s">
@@ -5847,7 +5887,7 @@
       <c r="R30" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="S30" s="75" t="s">
+      <c r="S30" s="63" t="s">
         <v>639</v>
       </c>
       <c r="T30" s="32"/>
@@ -5892,7 +5932,7 @@
       <c r="N31" s="32" t="s">
         <v>541</v>
       </c>
-      <c r="O31" s="75" t="s">
+      <c r="O31" s="63" t="s">
         <v>638</v>
       </c>
       <c r="P31" s="32" t="s">
@@ -5904,7 +5944,7 @@
       <c r="R31" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="S31" s="75" t="s">
+      <c r="S31" s="63" t="s">
         <v>639</v>
       </c>
       <c r="T31" s="32"/>
@@ -6725,9 +6765,7 @@
       <c r="K53" s="32" t="s">
         <v>504</v>
       </c>
-      <c r="L53" s="32" t="s">
-        <v>640</v>
-      </c>
+      <c r="L53" s="32"/>
       <c r="M53" s="32"/>
       <c r="N53" s="32"/>
       <c r="O53" s="32"/>
@@ -6775,13 +6813,25 @@
       </c>
       <c r="K54" s="32"/>
       <c r="L54" s="32"/>
-      <c r="M54" s="32"/>
-      <c r="N54" s="32"/>
+      <c r="M54" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="N54" s="32" t="s">
+        <v>75</v>
+      </c>
       <c r="O54" s="32"/>
-      <c r="P54" s="32"/>
-      <c r="Q54" s="32"/>
-      <c r="R54" s="32"/>
-      <c r="S54" s="32"/>
+      <c r="P54" s="64" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q54" s="64" t="s">
+        <v>75</v>
+      </c>
+      <c r="R54" s="64" t="s">
+        <v>75</v>
+      </c>
+      <c r="S54" s="32" t="s">
+        <v>671</v>
+      </c>
       <c r="T54" s="32"/>
       <c r="U54" s="33"/>
       <c r="V54" s="34"/>
@@ -6815,15 +6865,13 @@
       <c r="K55" s="32" t="s">
         <v>504</v>
       </c>
-      <c r="L55" s="32" t="s">
-        <v>644</v>
-      </c>
+      <c r="L55" s="32"/>
       <c r="M55" s="32"/>
       <c r="N55" s="32"/>
       <c r="O55" s="32"/>
-      <c r="P55" s="32"/>
-      <c r="Q55" s="32"/>
-      <c r="R55" s="32"/>
+      <c r="P55" s="65"/>
+      <c r="Q55" s="65"/>
+      <c r="R55" s="65"/>
       <c r="S55" s="32"/>
       <c r="T55" s="32"/>
       <c r="U55" s="33"/>
@@ -6865,13 +6913,25 @@
       </c>
       <c r="K56" s="32"/>
       <c r="L56" s="32"/>
-      <c r="M56" s="32"/>
-      <c r="N56" s="32"/>
+      <c r="M56" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="N56" s="32" t="s">
+        <v>75</v>
+      </c>
       <c r="O56" s="32"/>
-      <c r="P56" s="32"/>
-      <c r="Q56" s="32"/>
-      <c r="R56" s="32"/>
-      <c r="S56" s="32"/>
+      <c r="P56" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q56" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="R56" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="S56" s="32" t="s">
+        <v>671</v>
+      </c>
       <c r="T56" s="32"/>
       <c r="U56" s="33"/>
       <c r="V56" s="34"/>
@@ -6905,15 +6965,13 @@
       <c r="K57" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="L57" s="32" t="s">
-        <v>648</v>
-      </c>
+      <c r="L57" s="32"/>
       <c r="M57" s="32"/>
       <c r="N57" s="32"/>
       <c r="O57" s="32"/>
-      <c r="P57" s="32"/>
-      <c r="Q57" s="32"/>
-      <c r="R57" s="32"/>
+      <c r="P57" s="65"/>
+      <c r="Q57" s="65"/>
+      <c r="R57" s="65"/>
       <c r="S57" s="32"/>
       <c r="T57" s="32"/>
       <c r="U57" s="33"/>
@@ -6949,14 +7007,14 @@
         <v>505</v>
       </c>
       <c r="L58" s="32" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="M58" s="32"/>
       <c r="N58" s="32"/>
       <c r="O58" s="32"/>
-      <c r="P58" s="32"/>
-      <c r="Q58" s="32"/>
-      <c r="R58" s="32"/>
+      <c r="P58" s="65"/>
+      <c r="Q58" s="65"/>
+      <c r="R58" s="65"/>
       <c r="S58" s="32"/>
       <c r="T58" s="32"/>
       <c r="U58" s="33"/>
@@ -6992,14 +7050,14 @@
         <v>505</v>
       </c>
       <c r="L59" s="32" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="M59" s="32"/>
       <c r="N59" s="32"/>
       <c r="O59" s="32"/>
-      <c r="P59" s="32"/>
-      <c r="Q59" s="32"/>
-      <c r="R59" s="32"/>
+      <c r="P59" s="65"/>
+      <c r="Q59" s="65"/>
+      <c r="R59" s="65"/>
       <c r="S59" s="32"/>
       <c r="T59" s="32"/>
       <c r="U59" s="33"/>
@@ -7028,26 +7086,38 @@
         <v>46069</v>
       </c>
       <c r="G60" s="31" t="s">
+        <v>650</v>
+      </c>
+      <c r="H60" s="31" t="s">
         <v>651</v>
       </c>
-      <c r="H60" s="31" t="s">
+      <c r="I60" s="36" t="s">
         <v>652</v>
-      </c>
-      <c r="I60" s="36" t="s">
-        <v>653</v>
       </c>
       <c r="J60" s="32" t="s">
         <v>75</v>
       </c>
       <c r="K60" s="32"/>
       <c r="L60" s="32"/>
-      <c r="M60" s="32"/>
-      <c r="N60" s="32"/>
+      <c r="M60" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="N60" s="32" t="s">
+        <v>75</v>
+      </c>
       <c r="O60" s="32"/>
-      <c r="P60" s="32"/>
-      <c r="Q60" s="32"/>
-      <c r="R60" s="32"/>
-      <c r="S60" s="32"/>
+      <c r="P60" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q60" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="R60" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="S60" s="32" t="s">
+        <v>671</v>
+      </c>
       <c r="T60" s="32"/>
       <c r="U60" s="33"/>
       <c r="V60" s="34"/>
@@ -7081,9 +7151,7 @@
       <c r="K61" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="L61" s="32" t="s">
-        <v>654</v>
-      </c>
+      <c r="L61" s="32"/>
       <c r="M61" s="32"/>
       <c r="N61" s="32"/>
       <c r="O61" s="32"/>
@@ -7124,9 +7192,7 @@
       <c r="K62" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="L62" s="32" t="s">
-        <v>654</v>
-      </c>
+      <c r="L62" s="32"/>
       <c r="M62" s="32"/>
       <c r="N62" s="32"/>
       <c r="O62" s="32"/>
@@ -7167,9 +7233,7 @@
       <c r="K63" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="L63" s="32" t="s">
-        <v>654</v>
-      </c>
+      <c r="L63" s="32"/>
       <c r="M63" s="32"/>
       <c r="N63" s="32"/>
       <c r="O63" s="32"/>
@@ -7210,9 +7274,7 @@
       <c r="K64" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="L64" s="32" t="s">
-        <v>654</v>
-      </c>
+      <c r="L64" s="32"/>
       <c r="M64" s="32"/>
       <c r="N64" s="32"/>
       <c r="O64" s="32"/>
@@ -7253,9 +7315,7 @@
       <c r="K65" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="L65" s="32" t="s">
-        <v>654</v>
-      </c>
+      <c r="L65" s="32"/>
       <c r="M65" s="32"/>
       <c r="N65" s="32"/>
       <c r="O65" s="32"/>
@@ -7296,9 +7356,7 @@
       <c r="K66" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="L66" s="32" t="s">
-        <v>654</v>
-      </c>
+      <c r="L66" s="32"/>
       <c r="M66" s="32"/>
       <c r="N66" s="32"/>
       <c r="O66" s="32"/>
@@ -7339,9 +7397,7 @@
       <c r="K67" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="L67" s="32" t="s">
-        <v>655</v>
-      </c>
+      <c r="L67" s="32"/>
       <c r="M67" s="32"/>
       <c r="N67" s="32"/>
       <c r="O67" s="32"/>
@@ -7382,9 +7438,7 @@
       <c r="K68" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="L68" s="32" t="s">
-        <v>654</v>
-      </c>
+      <c r="L68" s="32"/>
       <c r="M68" s="32"/>
       <c r="N68" s="32"/>
       <c r="O68" s="32"/>
@@ -9201,13 +9255,13 @@
         <v>46069</v>
       </c>
       <c r="G117" s="31" t="s">
+        <v>654</v>
+      </c>
+      <c r="H117" s="31" t="s">
+        <v>655</v>
+      </c>
+      <c r="I117" s="36" t="s">
         <v>656</v>
-      </c>
-      <c r="H117" s="31" t="s">
-        <v>657</v>
-      </c>
-      <c r="I117" s="36" t="s">
-        <v>658</v>
       </c>
       <c r="J117" s="32" t="s">
         <v>75</v>
@@ -9291,13 +9345,13 @@
         <v>46069</v>
       </c>
       <c r="G119" s="31" t="s">
+        <v>657</v>
+      </c>
+      <c r="H119" s="31" t="s">
+        <v>658</v>
+      </c>
+      <c r="I119" s="36" t="s">
         <v>659</v>
-      </c>
-      <c r="H119" s="31" t="s">
-        <v>660</v>
-      </c>
-      <c r="I119" s="36" t="s">
-        <v>661</v>
       </c>
       <c r="J119" s="32" t="s">
         <v>75</v>
@@ -9345,7 +9399,7 @@
         <v>505</v>
       </c>
       <c r="L120" s="32" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="M120" s="32"/>
       <c r="N120" s="32"/>
@@ -9388,7 +9442,7 @@
         <v>505</v>
       </c>
       <c r="L121" s="32" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="M121" s="32"/>
       <c r="N121" s="32"/>
@@ -9424,13 +9478,13 @@
         <v>46069</v>
       </c>
       <c r="G122" s="31" t="s">
+        <v>661</v>
+      </c>
+      <c r="H122" s="31" t="s">
+        <v>662</v>
+      </c>
+      <c r="I122" s="36" t="s">
         <v>663</v>
-      </c>
-      <c r="H122" s="31" t="s">
-        <v>664</v>
-      </c>
-      <c r="I122" s="36" t="s">
-        <v>665</v>
       </c>
       <c r="J122" s="32" t="s">
         <v>75</v>
@@ -9478,7 +9532,7 @@
         <v>499</v>
       </c>
       <c r="L123" s="32" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="M123" s="32"/>
       <c r="N123" s="32"/>
@@ -9521,7 +9575,7 @@
         <v>499</v>
       </c>
       <c r="L124" s="32" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="M124" s="32"/>
       <c r="N124" s="32"/>
@@ -9556,14 +9610,14 @@
       <c r="F125" s="31">
         <v>46065</v>
       </c>
-      <c r="G125" s="72">
+      <c r="G125" s="60">
         <v>46065.611481481479</v>
       </c>
       <c r="H125" s="31" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="I125" s="36" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="J125" s="32" t="s">
         <v>75</v>
@@ -9580,7 +9634,7 @@
       <c r="T125" s="32"/>
       <c r="U125" s="33"/>
       <c r="V125" s="34" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="W125" s="32" t="s">
         <v>46</v>
@@ -9613,7 +9667,7 @@
         <v>499</v>
       </c>
       <c r="L126" s="32" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="M126" s="32"/>
       <c r="N126" s="32"/>
@@ -9656,7 +9710,7 @@
         <v>499</v>
       </c>
       <c r="L127" s="32" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="M127" s="32"/>
       <c r="N127" s="32"/>
@@ -9699,7 +9753,7 @@
         <v>499</v>
       </c>
       <c r="L128" s="32" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="M128" s="32"/>
       <c r="N128" s="32"/>
@@ -9742,7 +9796,7 @@
         <v>499</v>
       </c>
       <c r="L129" s="32" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="M129" s="32"/>
       <c r="N129" s="32"/>
@@ -9785,7 +9839,7 @@
         <v>504</v>
       </c>
       <c r="L130" s="32" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="M130" s="32"/>
       <c r="N130" s="32"/>
@@ -11040,11 +11094,21 @@
       <c r="E164" s="37" t="s">
         <v>341</v>
       </c>
-      <c r="F164" s="31"/>
-      <c r="G164" s="31"/>
-      <c r="H164" s="31"/>
-      <c r="I164" s="36"/>
-      <c r="J164" s="32"/>
+      <c r="F164" s="31">
+        <v>46065</v>
+      </c>
+      <c r="G164" s="60">
+        <v>46065.612395833334</v>
+      </c>
+      <c r="H164" s="31" t="s">
+        <v>668</v>
+      </c>
+      <c r="I164" s="36" t="s">
+        <v>669</v>
+      </c>
+      <c r="J164" s="32" t="s">
+        <v>75</v>
+      </c>
       <c r="K164" s="32"/>
       <c r="L164" s="32"/>
       <c r="M164" s="32"/>
@@ -11495,7 +11559,7 @@
         <v>499</v>
       </c>
       <c r="L176" s="32" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="M176" s="32"/>
       <c r="N176" s="32"/>
@@ -11537,9 +11601,7 @@
       <c r="K177" s="32" t="s">
         <v>504</v>
       </c>
-      <c r="L177" s="32" t="s">
-        <v>669</v>
-      </c>
+      <c r="L177" s="32"/>
       <c r="M177" s="32"/>
       <c r="N177" s="32"/>
       <c r="O177" s="29"/>
@@ -11766,7 +11828,7 @@
         <v>504</v>
       </c>
       <c r="L183" s="32" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="M183" s="32"/>
       <c r="N183" s="32"/>
@@ -11875,14 +11937,14 @@
       <c r="F186" s="31">
         <v>46065</v>
       </c>
-      <c r="G186" s="72">
+      <c r="G186" s="60">
         <v>46065.612395833334</v>
       </c>
       <c r="H186" s="31" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I186" s="36" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J186" s="32" t="s">
         <v>75</v>
@@ -11899,7 +11961,7 @@
       <c r="T186" s="32"/>
       <c r="U186" s="33"/>
       <c r="V186" s="34" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="W186" s="32" t="s">
         <v>46</v>
@@ -11931,9 +11993,7 @@
       <c r="K187" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="L187" s="32" t="s">
-        <v>654</v>
-      </c>
+      <c r="L187" s="32"/>
       <c r="M187" s="32"/>
       <c r="N187" s="32"/>
       <c r="O187" s="32"/>
@@ -12011,9 +12071,7 @@
       <c r="K189" s="32" t="s">
         <v>504</v>
       </c>
-      <c r="L189" s="32" t="s">
-        <v>672</v>
-      </c>
+      <c r="L189" s="32"/>
       <c r="M189" s="32"/>
       <c r="N189" s="32"/>
       <c r="O189" s="32"/>
@@ -12055,7 +12113,7 @@
         <v>504</v>
       </c>
       <c r="L190" s="32" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="M190" s="32"/>
       <c r="N190" s="32"/>
@@ -17798,24 +17856,24 @@
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{F5F4AC7B-142E-4F14-AD0B-95E75DB6B433}">
           <x14:formula1>
             <xm:f>Sheet1!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>P191:R285 J191:J285 M10:N13 J10:J13 P10:R13 P16:R21 M16:N21 J16:J21 J24:J29 P24:R29 M24:N29 M32:N52 J32:J52 P32:R52 P69:R115 M69:N115 J69:J115 J131:J175 P131:R175 M131:N175 M178:N182 J178:J182 P178:R182 P184:R185 M184:N185 J184:J185 J188 P188:R188 M188:N188 M191:N285</xm:sqref>
+          <xm:sqref>P191:R285 J191:J285 M10:N13 J10:J13 P10:R13 P16:R21 M16:N21 J16:J21 J24:J29 P24:R29 M24:N29 M32:N52 J32:J52 P32:R52 P69:R115 M69:N115 J69:J115 P165:R175 M165:N175 M191:N285 M178:N182 J178:J182 P178:R182 P184:R185 M184:N185 J184:J185 J188 P188:R188 M188:N188 M131:N163 P131:R163 J131:J163 J165:J175</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{70793024-27E9-4E6A-BACD-083AB683BC38}">
           <x14:formula1>
             <xm:f>Sheet1!$A$2:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>T10:T13 T16:T21 T24:T29 T32:T52 T69:T115 T131:T175 T178:T182 T184:T185 T188 T191:T285</xm:sqref>
+          <xm:sqref>T10:T13 T16:T21 T24:T29 T32:T52 T69:T115 T191:T285 T178:T182 T184:T185 T188 T131:T163 T165:T175</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3DE61C5E-9DA3-4CE3-A1FF-8FBE651EA6B5}">
           <x14:formula1>
             <xm:f>'LISTA VALORI'!$A$2:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>K10:K13 K16:K21 K24:K29 K32:K52 K69:K115 K131:K175 K178:K182 K184:K185 K188 K191:K285</xm:sqref>
+          <xm:sqref>K10:K13 K16:K21 K24:K29 K32:K52 K69:K115 K191:K285 K178:K182 K184:K185 K188 K131:K163 K165:K175</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -20126,27 +20184,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A92AB09DCDF6014AA0D6826BF29E2C8E" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="58b13f75919cba2dcad85f84b1d5db00">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e76d14e-d0ce-457c-8343-9b55836d9ead" xmlns:ns3="a56712a3-8dfd-4688-917a-22f0cf513b89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3b16ea44285e6579c272a3325f660d0" ns2:_="" ns3:_="">
     <xsd:import namespace="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
@@ -20410,32 +20447,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD72871-87C6-44C4-AEDE-C35BE2C233EE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20454,6 +20487,31 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e0793d39-0939-496d-b129-198edd916feb}" enabled="0" method="" siteId="{e0793d39-0939-496d-b129-198edd916feb}" removed="1"/>

--- a/GATEWAY/A1#111#DOCPLANNERXX/DOCPLANNER_ITALY/MioDottore/1/report-checklist.xlsx
+++ b/GATEWAY/A1#111#DOCPLANNERXX/DOCPLANNER_ITALY/MioDottore/1/report-checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincenzo.camerino/Documents/Obsidian notes/GIPO/SSN/FSE 2.0/Accreditamento GTW/Accreditamento MioDottore/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BAD4ACE-FC58-9447-BAA4-F2FF8B770BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AEF1EA-8589-3545-9FC5-45BFEA6FDF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="600" windowWidth="19160" windowHeight="19220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6440" yWindow="1460" windowWidth="19180" windowHeight="19220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -58,15 +58,41 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>======
-ID#AAAAzAuRGEo
-    (2023-06-14 09:12:48)
-Ove non specificate le precondizioni del caso di test possono essere recuperate nel tab "Prerequisiti"</t>
+          <t xml:space="preserve">======
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ID#AAAAzAuRGEo
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">    (2023-06-14 09:12:48)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>Ove non specificate le precondizioni del caso di test possono essere recuperate nel tab "Prerequisiti"</t>
         </r>
       </text>
     </comment>
@@ -80,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="671">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -2443,9 +2469,6 @@
     <t>Dopo un certo numero di tentativi falliti, l'operatore di backoffice avrà la possibilità di ricollocare manualmente il documento nella coda di invio a FSE</t>
   </si>
   <si>
-    <t>L'applicativo non consente la registrazione di caratteri minuscoli nel CF</t>
-  </si>
-  <si>
     <t>02/16/2026 13:32:21 +00:00</t>
   </si>
   <si>
@@ -2455,9 +2478,6 @@
     <t>2.16.840.1.113883.2.9.2.120.4.4.e5050b445fba6edcd254bc0f4cc47857cfa82cd5b8591c9008c6d5531af7c80f.6ebbac46e9^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
-    <t>L'applicativo non consente la registrazione di pazienti senza nome o cognome</t>
-  </si>
-  <si>
     <t>02/16/2026 13:49:24 +00:00</t>
   </si>
   <si>
@@ -2515,28 +2535,31 @@
     <t>2.16.840.1.113883.2.9.2.120.4.4.2f5bc75e8c1b2e37758fcfa7106f3f90e9cce1679730d6ac2445d1784899fb9d.eecd808db4^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
-    <t>L'applicativo non consente una valorizzazione diversa da S</t>
-  </si>
-  <si>
     <t>a30ae95d4318ca884640c70d49af0813</t>
   </si>
   <si>
     <t xml:space="preserve"> 2.16.840.1.113883.2.9.2.120.4.4.d4867bf5f803aecea5da0509d2fa651d0b9f7fc08ea5a9fc104e0678b1819acb.3e7b44ed34^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
-    <t>L'applicativo non consente di non impostare il livello di riservatezza</t>
-  </si>
-  <si>
     <t>a914c86ece2f2c586bb61f2a24d7c580</t>
   </si>
   <si>
     <t>2.16.840.1.113883.2.9.2.120.4.4.fc63ec2e411efeb0dfffe15094d2e6c5a21aea81f880958987f5e43af148f094.745da8003b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
-    <t>L'applicativo non consente la registrazione di codici non previsti</t>
-  </si>
-  <si>
     <t>Dopo un certo numero di tentativi falliti, l'operatore di backoffice avrà la possibilità di risolvere l'anomalia e ricollocare manualmente il documento nella coda di invio a FSE</t>
+  </si>
+  <si>
+    <t>Token non valido</t>
+  </si>
+  <si>
+    <t>Indirizzo incompleto</t>
+  </si>
+  <si>
+    <t>administrativeGenderCode non valido</t>
+  </si>
+  <si>
+    <t>Il testo del referto è obbligatorio</t>
   </si>
 </sst>
 </file>
@@ -2546,7 +2569,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2676,6 +2699,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -5225,7 +5254,9 @@
       <c r="N14" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="O14" s="32"/>
+      <c r="O14" s="32" t="s">
+        <v>667</v>
+      </c>
       <c r="P14" s="32" t="s">
         <v>75</v>
       </c>
@@ -5236,7 +5267,7 @@
         <v>75</v>
       </c>
       <c r="S14" s="32" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="T14" s="32"/>
       <c r="U14" s="33"/>
@@ -5276,13 +5307,27 @@
       </c>
       <c r="K15" s="32"/>
       <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="32"/>
-      <c r="O15" s="32"/>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="32"/>
-      <c r="R15" s="32"/>
-      <c r="S15" s="32"/>
+      <c r="M15" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="N15" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="O15" s="32" t="s">
+        <v>667</v>
+      </c>
+      <c r="P15" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q15" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="R15" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="S15" s="32" t="s">
+        <v>666</v>
+      </c>
       <c r="T15" s="32"/>
       <c r="U15" s="33"/>
       <c r="V15" s="34"/>
@@ -5549,7 +5594,9 @@
       <c r="N22" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="O22" s="32"/>
+      <c r="O22" s="32" t="s">
+        <v>667</v>
+      </c>
       <c r="P22" s="32" t="s">
         <v>75</v>
       </c>
@@ -5560,7 +5607,7 @@
         <v>75</v>
       </c>
       <c r="S22" s="32" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="T22" s="32"/>
       <c r="U22" s="33"/>
@@ -5600,13 +5647,27 @@
       </c>
       <c r="K23" s="32"/>
       <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="32"/>
-      <c r="O23" s="32"/>
-      <c r="P23" s="32"/>
-      <c r="Q23" s="32"/>
-      <c r="R23" s="32"/>
-      <c r="S23" s="32"/>
+      <c r="M23" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="N23" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="O23" s="32" t="s">
+        <v>667</v>
+      </c>
+      <c r="P23" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q23" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="R23" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="S23" s="32" t="s">
+        <v>666</v>
+      </c>
       <c r="T23" s="32"/>
       <c r="U23" s="33"/>
       <c r="V23" s="34"/>
@@ -6800,13 +6861,13 @@
         <v>46069</v>
       </c>
       <c r="G54" s="31" t="s">
+        <v>640</v>
+      </c>
+      <c r="H54" s="31" t="s">
         <v>641</v>
       </c>
-      <c r="H54" s="31" t="s">
+      <c r="I54" s="36" t="s">
         <v>642</v>
-      </c>
-      <c r="I54" s="36" t="s">
-        <v>643</v>
       </c>
       <c r="J54" s="32" t="s">
         <v>75</v>
@@ -6819,7 +6880,9 @@
       <c r="N54" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="O54" s="32"/>
+      <c r="O54" s="32" t="s">
+        <v>668</v>
+      </c>
       <c r="P54" s="64" t="s">
         <v>75</v>
       </c>
@@ -6830,7 +6893,7 @@
         <v>75</v>
       </c>
       <c r="S54" s="32" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="T54" s="32"/>
       <c r="U54" s="33"/>
@@ -6900,13 +6963,13 @@
         <v>46069</v>
       </c>
       <c r="G56" s="31" t="s">
+        <v>643</v>
+      </c>
+      <c r="H56" s="31" t="s">
+        <v>644</v>
+      </c>
+      <c r="I56" s="36" t="s">
         <v>645</v>
-      </c>
-      <c r="H56" s="31" t="s">
-        <v>646</v>
-      </c>
-      <c r="I56" s="36" t="s">
-        <v>647</v>
       </c>
       <c r="J56" s="32" t="s">
         <v>75</v>
@@ -6919,7 +6982,9 @@
       <c r="N56" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="O56" s="32"/>
+      <c r="O56" s="32" t="s">
+        <v>669</v>
+      </c>
       <c r="P56" s="65" t="s">
         <v>75</v>
       </c>
@@ -6930,7 +6995,7 @@
         <v>75</v>
       </c>
       <c r="S56" s="32" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="T56" s="32"/>
       <c r="U56" s="33"/>
@@ -7007,7 +7072,7 @@
         <v>505</v>
       </c>
       <c r="L58" s="32" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="M58" s="32"/>
       <c r="N58" s="32"/>
@@ -7050,7 +7115,7 @@
         <v>505</v>
       </c>
       <c r="L59" s="32" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="M59" s="32"/>
       <c r="N59" s="32"/>
@@ -7086,13 +7151,13 @@
         <v>46069</v>
       </c>
       <c r="G60" s="31" t="s">
+        <v>648</v>
+      </c>
+      <c r="H60" s="31" t="s">
+        <v>649</v>
+      </c>
+      <c r="I60" s="36" t="s">
         <v>650</v>
-      </c>
-      <c r="H60" s="31" t="s">
-        <v>651</v>
-      </c>
-      <c r="I60" s="36" t="s">
-        <v>652</v>
       </c>
       <c r="J60" s="32" t="s">
         <v>75</v>
@@ -7105,7 +7170,9 @@
       <c r="N60" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="O60" s="32"/>
+      <c r="O60" s="32" t="s">
+        <v>670</v>
+      </c>
       <c r="P60" s="65" t="s">
         <v>75</v>
       </c>
@@ -7116,7 +7183,7 @@
         <v>75</v>
       </c>
       <c r="S60" s="32" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="T60" s="32"/>
       <c r="U60" s="33"/>
@@ -9218,9 +9285,7 @@
       <c r="K116" s="32" t="s">
         <v>504</v>
       </c>
-      <c r="L116" s="32" t="s">
-        <v>640</v>
-      </c>
+      <c r="L116" s="32"/>
       <c r="M116" s="32"/>
       <c r="N116" s="32"/>
       <c r="O116" s="32"/>
@@ -9255,26 +9320,40 @@
         <v>46069</v>
       </c>
       <c r="G117" s="31" t="s">
+        <v>652</v>
+      </c>
+      <c r="H117" s="31" t="s">
+        <v>653</v>
+      </c>
+      <c r="I117" s="36" t="s">
         <v>654</v>
-      </c>
-      <c r="H117" s="31" t="s">
-        <v>655</v>
-      </c>
-      <c r="I117" s="36" t="s">
-        <v>656</v>
       </c>
       <c r="J117" s="32" t="s">
         <v>75</v>
       </c>
       <c r="K117" s="32"/>
       <c r="L117" s="32"/>
-      <c r="M117" s="32"/>
-      <c r="N117" s="32"/>
-      <c r="O117" s="32"/>
-      <c r="P117" s="32"/>
-      <c r="Q117" s="32"/>
-      <c r="R117" s="32"/>
-      <c r="S117" s="32"/>
+      <c r="M117" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="N117" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="O117" s="32" t="s">
+        <v>668</v>
+      </c>
+      <c r="P117" s="64" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q117" s="64" t="s">
+        <v>75</v>
+      </c>
+      <c r="R117" s="64" t="s">
+        <v>75</v>
+      </c>
+      <c r="S117" s="32" t="s">
+        <v>666</v>
+      </c>
       <c r="T117" s="32"/>
       <c r="U117" s="33"/>
       <c r="V117" s="34"/>
@@ -9308,9 +9387,7 @@
       <c r="K118" s="32" t="s">
         <v>504</v>
       </c>
-      <c r="L118" s="32" t="s">
-        <v>644</v>
-      </c>
+      <c r="L118" s="32"/>
       <c r="M118" s="32"/>
       <c r="N118" s="32"/>
       <c r="O118" s="32"/>
@@ -9345,26 +9422,40 @@
         <v>46069</v>
       </c>
       <c r="G119" s="31" t="s">
+        <v>655</v>
+      </c>
+      <c r="H119" s="31" t="s">
+        <v>656</v>
+      </c>
+      <c r="I119" s="36" t="s">
         <v>657</v>
-      </c>
-      <c r="H119" s="31" t="s">
-        <v>658</v>
-      </c>
-      <c r="I119" s="36" t="s">
-        <v>659</v>
       </c>
       <c r="J119" s="32" t="s">
         <v>75</v>
       </c>
       <c r="K119" s="32"/>
       <c r="L119" s="32"/>
-      <c r="M119" s="32"/>
-      <c r="N119" s="32"/>
-      <c r="O119" s="32"/>
-      <c r="P119" s="32"/>
-      <c r="Q119" s="32"/>
-      <c r="R119" s="32"/>
-      <c r="S119" s="32"/>
+      <c r="M119" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="N119" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="O119" s="32" t="s">
+        <v>669</v>
+      </c>
+      <c r="P119" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q119" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="R119" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="S119" s="32" t="s">
+        <v>666</v>
+      </c>
       <c r="T119" s="32"/>
       <c r="U119" s="33"/>
       <c r="V119" s="34"/>
@@ -9399,7 +9490,7 @@
         <v>505</v>
       </c>
       <c r="L120" s="32" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="M120" s="32"/>
       <c r="N120" s="32"/>
@@ -9442,7 +9533,7 @@
         <v>505</v>
       </c>
       <c r="L121" s="32" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="M121" s="32"/>
       <c r="N121" s="32"/>
@@ -9478,26 +9569,40 @@
         <v>46069</v>
       </c>
       <c r="G122" s="31" t="s">
+        <v>659</v>
+      </c>
+      <c r="H122" s="31" t="s">
+        <v>660</v>
+      </c>
+      <c r="I122" s="36" t="s">
         <v>661</v>
-      </c>
-      <c r="H122" s="31" t="s">
-        <v>662</v>
-      </c>
-      <c r="I122" s="36" t="s">
-        <v>663</v>
       </c>
       <c r="J122" s="32" t="s">
         <v>75</v>
       </c>
       <c r="K122" s="32"/>
       <c r="L122" s="32"/>
-      <c r="M122" s="32"/>
-      <c r="N122" s="32"/>
-      <c r="O122" s="32"/>
-      <c r="P122" s="32"/>
-      <c r="Q122" s="32"/>
-      <c r="R122" s="32"/>
-      <c r="S122" s="32"/>
+      <c r="M122" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="N122" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="O122" s="32" t="s">
+        <v>670</v>
+      </c>
+      <c r="P122" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q122" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="R122" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="S122" s="32" t="s">
+        <v>666</v>
+      </c>
       <c r="T122" s="32"/>
       <c r="U122" s="33"/>
       <c r="V122" s="34"/>
@@ -9531,9 +9636,7 @@
       <c r="K123" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="L123" s="32" t="s">
-        <v>653</v>
-      </c>
+      <c r="L123" s="32"/>
       <c r="M123" s="32"/>
       <c r="N123" s="32"/>
       <c r="O123" s="32"/>
@@ -9574,9 +9677,7 @@
       <c r="K124" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="L124" s="32" t="s">
-        <v>653</v>
-      </c>
+      <c r="L124" s="32"/>
       <c r="M124" s="32"/>
       <c r="N124" s="32"/>
       <c r="O124" s="32"/>
@@ -9614,10 +9715,10 @@
         <v>46065.611481481479</v>
       </c>
       <c r="H125" s="31" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="I125" s="36" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="J125" s="32" t="s">
         <v>75</v>
@@ -9634,7 +9735,7 @@
       <c r="T125" s="32"/>
       <c r="U125" s="33"/>
       <c r="V125" s="34" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="W125" s="32" t="s">
         <v>46</v>
@@ -9666,9 +9767,7 @@
       <c r="K126" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="L126" s="32" t="s">
-        <v>653</v>
-      </c>
+      <c r="L126" s="32"/>
       <c r="M126" s="32"/>
       <c r="N126" s="32"/>
       <c r="O126" s="32"/>
@@ -9709,9 +9808,7 @@
       <c r="K127" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="L127" s="32" t="s">
-        <v>653</v>
-      </c>
+      <c r="L127" s="32"/>
       <c r="M127" s="32"/>
       <c r="N127" s="32"/>
       <c r="O127" s="32"/>
@@ -9752,9 +9849,7 @@
       <c r="K128" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="L128" s="32" t="s">
-        <v>653</v>
-      </c>
+      <c r="L128" s="32"/>
       <c r="M128" s="32"/>
       <c r="N128" s="32"/>
       <c r="O128" s="32"/>
@@ -9795,9 +9890,7 @@
       <c r="K129" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="L129" s="32" t="s">
-        <v>653</v>
-      </c>
+      <c r="L129" s="32"/>
       <c r="M129" s="32"/>
       <c r="N129" s="32"/>
       <c r="O129" s="32"/>
@@ -9838,9 +9931,7 @@
       <c r="K130" s="32" t="s">
         <v>504</v>
       </c>
-      <c r="L130" s="32" t="s">
-        <v>664</v>
-      </c>
+      <c r="L130" s="32"/>
       <c r="M130" s="32"/>
       <c r="N130" s="32"/>
       <c r="O130" s="32"/>
@@ -11101,10 +11192,10 @@
         <v>46065.612395833334</v>
       </c>
       <c r="H164" s="31" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="I164" s="36" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="J164" s="32" t="s">
         <v>75</v>
@@ -11145,8 +11236,12 @@
       <c r="G165" s="31"/>
       <c r="H165" s="31"/>
       <c r="I165" s="36"/>
-      <c r="J165" s="32"/>
-      <c r="K165" s="32"/>
+      <c r="J165" s="32" t="s">
+        <v>541</v>
+      </c>
+      <c r="K165" s="32" t="s">
+        <v>499</v>
+      </c>
       <c r="L165" s="32"/>
       <c r="M165" s="32"/>
       <c r="N165" s="32"/>
@@ -11558,9 +11653,7 @@
       <c r="K176" s="32" t="s">
         <v>499</v>
       </c>
-      <c r="L176" s="32" t="s">
-        <v>653</v>
-      </c>
+      <c r="L176" s="32"/>
       <c r="M176" s="32"/>
       <c r="N176" s="32"/>
       <c r="O176" s="29"/>
@@ -11827,9 +11920,7 @@
       <c r="K183" s="32" t="s">
         <v>504</v>
       </c>
-      <c r="L183" s="32" t="s">
-        <v>667</v>
-      </c>
+      <c r="L183" s="32"/>
       <c r="M183" s="32"/>
       <c r="N183" s="32"/>
       <c r="O183" s="29"/>
@@ -11941,10 +12032,10 @@
         <v>46065.612395833334</v>
       </c>
       <c r="H186" s="31" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="I186" s="36" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="J186" s="32" t="s">
         <v>75</v>
@@ -11961,7 +12052,7 @@
       <c r="T186" s="32"/>
       <c r="U186" s="33"/>
       <c r="V186" s="34" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="W186" s="32" t="s">
         <v>46</v>
@@ -12112,9 +12203,7 @@
       <c r="K190" s="32" t="s">
         <v>504</v>
       </c>
-      <c r="L190" s="32" t="s">
-        <v>670</v>
-      </c>
+      <c r="L190" s="32"/>
       <c r="M190" s="32"/>
       <c r="N190" s="32"/>
       <c r="O190" s="32"/>
@@ -17856,7 +17945,7 @@
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{F5F4AC7B-142E-4F14-AD0B-95E75DB6B433}">
           <x14:formula1>
             <xm:f>Sheet1!$B$2:$B$3</xm:f>
@@ -20184,6 +20273,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A92AB09DCDF6014AA0D6826BF29E2C8E" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="58b13f75919cba2dcad85f84b1d5db00">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e76d14e-d0ce-457c-8343-9b55836d9ead" xmlns:ns3="a56712a3-8dfd-4688-917a-22f0cf513b89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3b16ea44285e6579c272a3325f660d0" ns2:_="" ns3:_="">
     <xsd:import namespace="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
@@ -20447,18 +20548,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -20469,6 +20558,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD72871-87C6-44C4-AEDE-C35BE2C233EE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20487,23 +20593,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>

--- a/GATEWAY/A1#111#DOCPLANNERXX/DOCPLANNER_ITALY/MioDottore/1/report-checklist.xlsx
+++ b/GATEWAY/A1#111#DOCPLANNERXX/DOCPLANNER_ITALY/MioDottore/1/report-checklist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincenzo.camerino/Documents/Obsidian notes/GIPO/SSN/FSE 2.0/Accreditamento GTW/Accreditamento MioDottore/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AEF1EA-8589-3545-9FC5-45BFEA6FDF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FAC98DA-D3D7-B641-A1A7-9FAEED19D729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6440" yWindow="1460" windowWidth="19180" windowHeight="19220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1719" uniqueCount="671">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -9708,22 +9708,16 @@
       <c r="E125" s="37" t="s">
         <v>264</v>
       </c>
-      <c r="F125" s="31">
-        <v>46065</v>
-      </c>
-      <c r="G125" s="60">
-        <v>46065.611481481479</v>
-      </c>
-      <c r="H125" s="31" t="s">
-        <v>662</v>
-      </c>
-      <c r="I125" s="36" t="s">
-        <v>663</v>
-      </c>
+      <c r="F125" s="31"/>
+      <c r="G125" s="60"/>
+      <c r="H125" s="31"/>
+      <c r="I125" s="36"/>
       <c r="J125" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="K125" s="32"/>
+        <v>541</v>
+      </c>
+      <c r="K125" s="32" t="s">
+        <v>499</v>
+      </c>
       <c r="L125" s="32"/>
       <c r="M125" s="32"/>
       <c r="N125" s="32"/>
@@ -9734,11 +9728,9 @@
       <c r="S125" s="32"/>
       <c r="T125" s="32"/>
       <c r="U125" s="33"/>
-      <c r="V125" s="34" t="s">
-        <v>651</v>
-      </c>
+      <c r="V125" s="34"/>
       <c r="W125" s="32" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="126" spans="1:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -11189,13 +11181,13 @@
         <v>46065</v>
       </c>
       <c r="G164" s="60">
-        <v>46065.612395833334</v>
+        <v>46065.611481481479</v>
       </c>
       <c r="H164" s="31" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="I164" s="36" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="J164" s="32" t="s">
         <v>75</v>
@@ -20273,18 +20265,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A92AB09DCDF6014AA0D6826BF29E2C8E" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="58b13f75919cba2dcad85f84b1d5db00">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e76d14e-d0ce-457c-8343-9b55836d9ead" xmlns:ns3="a56712a3-8dfd-4688-917a-22f0cf513b89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3b16ea44285e6579c272a3325f660d0" ns2:_="" ns3:_="">
     <xsd:import namespace="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
@@ -20548,6 +20528,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -20558,23 +20550,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD72871-87C6-44C4-AEDE-C35BE2C233EE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20593,6 +20568,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
